--- a/ESAN_PROGRAMAS.xlsx
+++ b/ESAN_PROGRAMAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\LicenciasESAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5C26E9-7BBC-47C2-BF39-8DDBE709418C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DAA5C7-FBC1-4CC3-BC9D-DE9F17896B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{E41BC6D3-CFA2-4B6D-9115-25C8C27678C2}"/>
   </bookViews>
@@ -7262,7 +7262,7 @@
         <v>139</v>
       </c>
       <c r="B6" s="1">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -7276,7 +7276,7 @@
         <v>140</v>
       </c>
       <c r="B7" s="1">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -7432,23 +7432,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A268F3EE5883504B842C6FF6FA714344" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="24c7283a044b6286ea9493cf38000e93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839" xmlns:ns4="96063de7-2efb-4437-8f42-7630d7a923ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cd2420228dd1092571a1a6e62a80269c" ns3:_="" ns4:_="">
     <xsd:import namespace="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839"/>
@@ -7687,32 +7670,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B42736-FA66-4781-A7D2-2B3F7034F7B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96063de7-2efb-4437-8f42-7630d7a923ce"/>
-    <ds:schemaRef ds:uri="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BBD9190-9532-4181-B3FB-1F2CBA350D74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33975297-DD7C-4FE7-AEB9-FA1C76DAA875}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7729,4 +7704,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BBD9190-9532-4181-B3FB-1F2CBA350D74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B42736-FA66-4781-A7D2-2B3F7034F7B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96063de7-2efb-4437-8f42-7630d7a923ce"/>
+    <ds:schemaRef ds:uri="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ESAN_PROGRAMAS.xlsx
+++ b/ESAN_PROGRAMAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\LicenciasESAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DAA5C7-FBC1-4CC3-BC9D-DE9F17896B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC15E76-8E58-457F-BC3A-1139B146AAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{E41BC6D3-CFA2-4B6D-9115-25C8C27678C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E41BC6D3-CFA2-4B6D-9115-25C8C27678C2}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="165">
   <si>
     <t>Item</t>
   </si>
@@ -499,18 +499,6 @@
     <t>B-403</t>
   </si>
   <si>
-    <t>A-301 (Robotica)</t>
-  </si>
-  <si>
-    <t>Laboratorio</t>
-  </si>
-  <si>
-    <t>Capacidad</t>
-  </si>
-  <si>
-    <t>A-302 (Robotica)</t>
-  </si>
-  <si>
     <t>PISO</t>
   </si>
   <si>
@@ -524,6 +512,33 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>TIPO LABORATORIO</t>
+  </si>
+  <si>
+    <t>CAPACIDAD</t>
+  </si>
+  <si>
+    <t>LABORATORIO</t>
+  </si>
+  <si>
+    <t>A-301</t>
+  </si>
+  <si>
+    <t>A-302</t>
+  </si>
+  <si>
+    <t>Robotica</t>
+  </si>
+  <si>
+    <t>Ingenieria</t>
+  </si>
+  <si>
+    <t>Ofimatica</t>
+  </si>
+  <si>
+    <t>Economia</t>
   </si>
 </sst>
 </file>
@@ -1408,7 +1423,7 @@
     <col min="5" max="5" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1443,10 +1458,10 @@
         <v>142</v>
       </c>
       <c r="L1" s="25" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M1" s="25" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>143</v>
@@ -7181,29 +7196,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7E3CB8-4DCD-4D5C-B503-8CB9BE47D4F8}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" t="s">
         <v>152</v>
       </c>
-      <c r="B1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
@@ -7212,12 +7231,15 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B3" s="1">
         <v>10</v>
@@ -7226,10 +7248,13 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>137</v>
       </c>
@@ -7240,10 +7265,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>138</v>
       </c>
@@ -7254,10 +7282,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>139</v>
       </c>
@@ -7268,10 +7299,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>140</v>
       </c>
@@ -7282,10 +7316,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>141</v>
       </c>
@@ -7296,10 +7333,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>142</v>
       </c>
@@ -7310,10 +7350,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="E9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>143</v>
       </c>
@@ -7324,10 +7367,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -7338,10 +7384,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>145</v>
       </c>
@@ -7352,10 +7401,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>146</v>
       </c>
@@ -7366,10 +7418,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>147</v>
       </c>
@@ -7380,10 +7435,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>148</v>
       </c>
@@ -7394,10 +7452,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="E15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>149</v>
       </c>
@@ -7408,10 +7469,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="E16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>150</v>
       </c>
@@ -7422,7 +7486,10 @@
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="E17" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/ESAN_PROGRAMAS.xlsx
+++ b/ESAN_PROGRAMAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\LicenciasESAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC15E76-8E58-457F-BC3A-1139B146AAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135720E8-658B-4586-888C-33C8BD5A163A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E41BC6D3-CFA2-4B6D-9115-25C8C27678C2}"/>
   </bookViews>
@@ -1709,7 +1709,7 @@
         <v>133</v>
       </c>
       <c r="E5" s="11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F5" s="31" t="s">
         <v>130</v>
@@ -1777,7 +1777,7 @@
         <v>133</v>
       </c>
       <c r="E6" s="11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F6" s="31" t="s">
         <v>130</v>
@@ -1845,7 +1845,7 @@
         <v>133</v>
       </c>
       <c r="E7" s="11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F7" s="31" t="s">
         <v>130</v>
@@ -4565,7 +4565,7 @@
         <v>133</v>
       </c>
       <c r="E47" s="11">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F47" s="32" t="s">
         <v>129</v>
@@ -7499,6 +7499,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A268F3EE5883504B842C6FF6FA714344" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="24c7283a044b6286ea9493cf38000e93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839" xmlns:ns4="96063de7-2efb-4437-8f42-7630d7a923ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cd2420228dd1092571a1a6e62a80269c" ns3:_="" ns4:_="">
     <xsd:import namespace="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839"/>
@@ -7737,24 +7754,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B42736-FA66-4781-A7D2-2B3F7034F7B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96063de7-2efb-4437-8f42-7630d7a923ce"/>
+    <ds:schemaRef ds:uri="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BBD9190-9532-4181-B3FB-1F2CBA350D74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33975297-DD7C-4FE7-AEB9-FA1C76DAA875}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7771,29 +7796,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BBD9190-9532-4181-B3FB-1F2CBA350D74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B42736-FA66-4781-A7D2-2B3F7034F7B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96063de7-2efb-4437-8f42-7630d7a923ce"/>
-    <ds:schemaRef ds:uri="c9bf7b5a-e1d9-4f15-8ed1-6069dd4bf839"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ESAN_PROGRAMAS.xlsx
+++ b/ESAN_PROGRAMAS.xlsx
@@ -10053,7 +10053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10227,6 +10227,28 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lcarrasco</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Luis Manuel Carrasco Paulini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
